--- a/evolution_rce_master/src/db/consumo_eletrico_agua.xlsx
+++ b/evolution_rce_master/src/db/consumo_eletrico_agua.xlsx
@@ -4,28 +4,59 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19740" windowHeight="7770"/>
+    <workbookView windowWidth="15360" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="Consumo Luz" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
-  <si>
-    <t>consumo</t>
-  </si>
-  <si>
-    <t>dias</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+  <si>
+    <t>Niteroi - ENEL</t>
+  </si>
+  <si>
+    <t>Campo Grande - Light</t>
+  </si>
+  <si>
+    <t>Consumo(KWH)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Preco/KWH</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>estacao do ano</t>
   </si>
   <si>
-    <t>preco</t>
+    <t>Preco Tributo</t>
+  </si>
+  <si>
+    <t>Preco Real</t>
+  </si>
+  <si>
+    <t>Taxa Acerto</t>
   </si>
   <si>
     <t>inverno</t>
@@ -38,19 +69,41 @@
   </si>
   <si>
     <t>primavera</t>
+  </si>
+  <si>
+    <t>cobranca_adicional</t>
+  </si>
+  <si>
+    <t>iluminacao_publica</t>
+  </si>
+  <si>
+    <t>preco_tributo</t>
+  </si>
+  <si>
+    <t>aliquota</t>
+  </si>
+  <si>
+    <t>confis</t>
+  </si>
+  <si>
+    <t>tarifa KWH</t>
+  </si>
+  <si>
+    <t>tributo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -59,31 +112,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -95,6 +135,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -113,14 +184,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -129,21 +192,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,8 +205,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,16 +221,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,15 +237,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,109 +280,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,31 +448,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,42 +460,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -413,11 +474,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -427,6 +509,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -442,21 +533,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -494,8 +570,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,212 +591,260 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
-    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
-    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
-    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
-    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
-    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
-    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
-    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
-    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
-    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
-    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
-    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
-    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
-    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
-    <cellStyle name="Saída" xfId="25" builtinId="21"/>
-    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
-    <cellStyle name="Total" xfId="27" builtinId="25"/>
-    <cellStyle name="Bom" xfId="28" builtinId="26"/>
-    <cellStyle name="40% - Ênfase 3" xfId="29" builtinId="39"/>
-    <cellStyle name="Texto de Aviso" xfId="30" builtinId="11"/>
-    <cellStyle name="Cálculo" xfId="31" builtinId="22"/>
-    <cellStyle name="Entrada" xfId="32" builtinId="20"/>
-    <cellStyle name="20% - Ênfase 2" xfId="33" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 1" xfId="34" builtinId="32"/>
-    <cellStyle name="Título 2" xfId="35" builtinId="17"/>
-    <cellStyle name="Texto Explicativo" xfId="36" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="37" builtinId="16"/>
-    <cellStyle name="Título" xfId="38" builtinId="15"/>
-    <cellStyle name="Observação" xfId="39" builtinId="10"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
-    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
-    <cellStyle name="Comma" xfId="43" builtinId="3"/>
-    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
-    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
-    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
-    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -989,159 +1113,512 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75" outlineLevelCol="3"/>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="15.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="12.7142857142857" customWidth="1"/>
+    <col min="4" max="5" width="14.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="4.71428571428571" customWidth="1"/>
+    <col min="7" max="7" width="18.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="9.57142857142857"/>
+    <col min="9" max="9" width="4" customWidth="1"/>
+    <col min="10" max="10" width="15.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="12.8571428571429"/>
+    <col min="13" max="13" width="14.2857142857143" customWidth="1"/>
+    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="15" max="15" width="10.7142857142857" customWidth="1"/>
+    <col min="16" max="16" width="13.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="16.5714285714286" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="4">
         <v>380</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B3" s="5">
         <v>45139</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
+      <c r="C3" s="6">
+        <f>A3*D8</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="J3" s="15">
+        <v>669</v>
+      </c>
+      <c r="K3" s="16">
+        <v>45352</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="15"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="4">
         <v>440</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B4" s="5">
         <v>45170</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
+      <c r="C4" s="6"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="J4" s="15">
+        <v>494</v>
+      </c>
+      <c r="K4" s="16">
+        <v>45383</v>
+      </c>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="15"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="4">
         <v>560</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="5">
         <v>45200</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
+      <c r="C5" s="6"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="J5" s="15">
+        <v>413</v>
+      </c>
+      <c r="K5" s="16">
+        <v>45413</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="4">
         <v>540</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="5">
         <v>45231</v>
       </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="C6" s="6"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="J6" s="15">
+        <v>453</v>
+      </c>
+      <c r="K6" s="16">
+        <v>45444</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="15"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="4">
         <v>690</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="5">
         <v>45261</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="J7" s="15">
+        <v>311</v>
+      </c>
+      <c r="K7" s="16">
+        <v>45474</v>
+      </c>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="15"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="4">
         <v>590</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="5">
         <v>45297</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="J8" s="15">
+        <v>369</v>
+      </c>
+      <c r="K8" s="16">
+        <v>45505</v>
+      </c>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="4">
         <v>560</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="5">
         <v>45329</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="J9" s="15">
+        <v>360</v>
+      </c>
+      <c r="K9" s="16">
+        <v>45536</v>
+      </c>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="15"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="4">
         <v>640</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="5">
         <v>45359</v>
       </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
+      <c r="C10" s="6"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="J10" s="15">
+        <v>462</v>
+      </c>
+      <c r="K10" s="16">
+        <v>45566</v>
+      </c>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="15"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="4">
         <v>560</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="5">
         <v>45391</v>
       </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
+      <c r="C11" s="6"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="J11" s="15">
+        <v>388</v>
+      </c>
+      <c r="K11" s="16">
+        <v>45597</v>
+      </c>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="4">
         <v>640</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="5">
         <v>45422</v>
       </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
+      <c r="C12" s="6"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="J12" s="15">
+        <v>554</v>
+      </c>
+      <c r="K12" s="16">
+        <v>45627</v>
+      </c>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="15"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="4">
         <v>590</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B13" s="5">
         <v>45444</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
+      <c r="C13" s="6"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="J13" s="15">
+        <v>617</v>
+      </c>
+      <c r="K13" s="16">
+        <v>45658</v>
+      </c>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="15"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="4">
         <v>670</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B14" s="5">
         <v>45474</v>
       </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="1"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="J14" s="15">
+        <v>598</v>
+      </c>
+      <c r="K14" s="16">
+        <v>45689</v>
+      </c>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="15"/>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="J15" s="17">
+        <v>968</v>
+      </c>
+      <c r="K15" s="16">
+        <v>45717</v>
+      </c>
+      <c r="L15" s="15">
+        <f>J15*H23</f>
+        <v>814.79464</v>
+      </c>
+      <c r="M15" s="15">
+        <f>H20*J15</f>
+        <v>1142.24</v>
+      </c>
+      <c r="N15" s="15">
+        <f>H18+H19+M15</f>
+        <v>1226.46</v>
+      </c>
+      <c r="O15" s="17">
+        <v>1228.81</v>
+      </c>
+      <c r="P15" s="18">
+        <f>(O15-N15)</f>
+        <v>2.34999999999991</v>
+      </c>
+      <c r="Q15" s="15"/>
+    </row>
+    <row r="16" spans="10:10">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="18" spans="6:8">
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8">
+      <c r="F19" s="10"/>
+      <c r="G19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="11">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8">
+      <c r="F20" s="10"/>
+      <c r="G20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="12">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="21" spans="7:8">
+      <c r="G21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="7:8">
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8">
+      <c r="F23" s="10"/>
+      <c r="G23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0.84173</v>
+      </c>
+    </row>
+    <row r="24" spans="7:8">
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="13">
+        <f>6/100</f>
+        <v>0.06</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="J1:Q1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
